--- a/Data/Jacobs/SummaryResultsV3U.xlsx
+++ b/Data/Jacobs/SummaryResultsV3U.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MMA\Projects\IS527200 Grattan Carbon\Markets\BQ125\Client\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/Jacobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCDDEA6D-405B-4449-8558-5647CBD2FF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BCDDEA6D-405B-4449-8558-5647CBD2FF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9468CB9A-A72D-4ECA-A170-27C980A295DE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{8DE268AB-E79B-4988-AC24-1187A77948EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{8DE268AB-E79B-4988-AC24-1187A77948EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Emissions" sheetId="1" r:id="rId1"/>

--- a/Data/Jacobs/SummaryResultsV3U.xlsx
+++ b/Data/Jacobs/SummaryResultsV3U.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unimelbcloud-my.sharepoint.com/personal/dominic_jones_grattaninstitute_edu_au/Documents/Energy/Analysis/analysis_cp_dj_2025/Data/Jacobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BCDDEA6D-405B-4449-8558-5647CBD2FF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9468CB9A-A72D-4ECA-A170-27C980A295DE}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{BCDDEA6D-405B-4449-8558-5647CBD2FF28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9633E78-C3D1-453A-ACF9-DD2B15CB76F7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{8DE268AB-E79B-4988-AC24-1187A77948EE}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{8DE268AB-E79B-4988-AC24-1187A77948EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Emissions" sheetId="1" r:id="rId1"/>
@@ -7726,7 +7726,7 @@
                   <c:v>70.55008122626657</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>55.544745737369908</c:v>
+                  <c:v>55.544745737369901</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>49.06569229604078</c:v>
@@ -19750,7 +19750,7 @@
         <v>70.55008122626657</v>
       </c>
       <c r="E8" s="2">
-        <v>55.544745737369908</v>
+        <v>55.544745737369901</v>
       </c>
       <c r="F8" s="2">
         <v>49.06569229604078</v>
